--- a/backend/data/uploads/MES/2026-07-18_불량현황.xlsx
+++ b/backend/data/uploads/MES/2026-07-18_불량현황.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sihoo\PythonProject\TestProject\backend\data\uploads\MES\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F114ADB3-422E-4CF2-A677-3513B1D6002F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{AA50E89B-C025-44F1-A667-D196B2166CDE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-30828" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{23FE8645-DCF1-4B71-A38D-7694F369F1D4}"/>
+    <workbookView xWindow="-30828" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{D8B9146E-DEBF-426A-8605-B54618404A7F}"/>
   </bookViews>
   <sheets>
     <sheet name="불량현황" sheetId="1" r:id="rId1"/>
@@ -492,7 +492,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{65703AD8-C4D7-44F3-8FFC-042A2B0E806C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0E275918-D5A5-4DE0-BE71-A5DBAFB7093F}">
   <dimension ref="B2:U12"/>
   <sheetFormatPr defaultRowHeight="17.600000000000001" x14ac:dyDescent="0.55000000000000004"/>
   <cols>

--- a/backend/data/uploads/MES/2026-07-18_불량현황.xlsx
+++ b/backend/data/uploads/MES/2026-07-18_불량현황.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sihoo\PythonProject\TestProject\backend\data\uploads\MES\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{AA50E89B-C025-44F1-A667-D196B2166CDE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D6B66633-93E0-4735-ACA9-94B68A9045D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-30828" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{D8B9146E-DEBF-426A-8605-B54618404A7F}"/>
+    <workbookView xWindow="-30828" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{9F5641A3-3D3C-4C8B-A743-61CC26EF1DFC}"/>
   </bookViews>
   <sheets>
     <sheet name="불량현황" sheetId="1" r:id="rId1"/>
@@ -492,7 +492,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0E275918-D5A5-4DE0-BE71-A5DBAFB7093F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{222BE4C3-6856-4D3F-B05E-061189BAC3A4}">
   <dimension ref="B2:U12"/>
   <sheetFormatPr defaultRowHeight="17.600000000000001" x14ac:dyDescent="0.55000000000000004"/>
   <cols>

--- a/backend/data/uploads/MES/2026-07-18_불량현황.xlsx
+++ b/backend/data/uploads/MES/2026-07-18_불량현황.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sihoo\PythonProject\TestProject\backend\data\uploads\MES\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D6B66633-93E0-4735-ACA9-94B68A9045D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D5D20879-AED5-4D6F-BFE4-4C160D253D95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-30828" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{9F5641A3-3D3C-4C8B-A743-61CC26EF1DFC}"/>
+    <workbookView xWindow="-30240" yWindow="8376" windowWidth="23040" windowHeight="12012" xr2:uid="{31DB24FB-437D-4DD6-B830-359F6C9221A7}"/>
   </bookViews>
   <sheets>
     <sheet name="불량현황" sheetId="1" r:id="rId1"/>
@@ -492,7 +492,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{222BE4C3-6856-4D3F-B05E-061189BAC3A4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27E64770-988A-4D3C-BFCB-044087FA6D20}">
   <dimension ref="B2:U12"/>
   <sheetFormatPr defaultRowHeight="17.600000000000001" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
